--- a/outputs/2026-08-20-development-plan/IconGen-开发计划.xlsx
+++ b/outputs/2026-08-20-development-plan/IconGen-开发计划.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阶段概览" sheetId="1" r:id="Rf022962e611d4cbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发任务总表" sheetId="2" r:id="Rcccbcf306c28411f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阶段概览" sheetId="1" r:id="Rdc1177eaf9cf47ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发任务总表" sheetId="2" r:id="R434c9bb97d2f43be"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -118,7 +118,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -128,7 +128,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -2480,7 +2480,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f03e30ee5054b80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23b3f60b8eef4246"/>
   </x:tableParts>
 </x:worksheet>
 </file>